--- a/resources/data-imports/World Gems/location-gems.xlsx
+++ b/resources/data-imports/World Gems/location-gems.xlsx
@@ -7,15 +7,15 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Location Gems" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="153">
   <si>
     <t>id</t>
   </si>
@@ -128,10 +128,10 @@
     <t>monster_atonement_range</t>
   </si>
   <si>
-    <t>Artificers Dreams</t>
-  </si>
-  <si>
-    <t>A legendary Artificer use to live in these caves before the shadows of their mind over whelmed them with visions of their death.</t>
+    <t>Shadow Caves Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Shadow Caves on Surface, raised five percent above its plane baseline.</t>
   </si>
   <si>
     <t>Surface</t>
@@ -140,52 +140,16 @@
     <t>Shadow Caves</t>
   </si>
   <si>
-    <t>Ring Crafting, Spell Crafting, Weapon Crafting</t>
-  </si>
-  <si>
-    <t>0.02-0.10</t>
-  </si>
-  <si>
-    <t>0.02-0.08</t>
-  </si>
-  <si>
-    <t>0.02-0.06</t>
-  </si>
-  <si>
-    <t>0.3-0.08</t>
-  </si>
-  <si>
-    <t>0.01-0.04</t>
-  </si>
-  <si>
-    <t>0.03-0.12</t>
-  </si>
-  <si>
-    <t>0.03-0.14</t>
-  </si>
-  <si>
-    <t>0.02-0.12</t>
-  </si>
-  <si>
-    <t>0.04-0.16</t>
-  </si>
-  <si>
-    <t>0.02-0.09</t>
-  </si>
-  <si>
-    <t>0.01-0.05</t>
-  </si>
-  <si>
-    <t>0.01-0.08</t>
-  </si>
-  <si>
-    <t>1.0-2.0</t>
-  </si>
-  <si>
-    <t>The Maze of the Mind</t>
-  </si>
-  <si>
-    <t>Entering deep into the mind of the maze, comes the challenges one never expected to solve or see manifest before them.</t>
+    <t>0.084-0.1575</t>
+  </si>
+  <si>
+    <t>0.063-0.126</t>
+  </si>
+  <si>
+    <t>Labyrinth Maze Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Labyrinth Maze on Labyrinth, raised five percent above its plane baseline.</t>
   </si>
   <si>
     <t>Labyrinth</t>
@@ -194,43 +158,10 @@
     <t>Labyrinth Maze</t>
   </si>
   <si>
-    <t>Armour Crafting, Disenchanting</t>
-  </si>
-  <si>
-    <t>0.03-0.13</t>
-  </si>
-  <si>
-    <t>0.02-0.16</t>
-  </si>
-  <si>
-    <t>0.05-0.13</t>
-  </si>
-  <si>
-    <t>0.03-0.08</t>
-  </si>
-  <si>
-    <t>0.03-0.09</t>
-  </si>
-  <si>
-    <t>0.02-0.14</t>
-  </si>
-  <si>
-    <t>0.06-0.18</t>
-  </si>
-  <si>
-    <t>0.06-0.19</t>
-  </si>
-  <si>
-    <t>0.04-0.15</t>
-  </si>
-  <si>
-    <t>2.00-4.00</t>
-  </si>
-  <si>
-    <t>The curse of the deranged</t>
-  </si>
-  <si>
-    <t>The Dungeons of Valifore are cursed by a magician who tried casting a spell to make him as powerful if not more so then, The Creator. I watched him burn his soul trying to reach this power and now he haunts this place.</t>
+    <t>Dungeons of Valifore Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Dungeons of Valifore on Dungeons, raised five percent above its plane baseline.</t>
   </si>
   <si>
     <t>Dungeons</t>
@@ -239,43 +170,310 @@
     <t>Dungeons of Valifore</t>
   </si>
   <si>
-    <t>Armour Crafting, Enchanting</t>
-  </si>
-  <si>
-    <t>0.03-0.18</t>
-  </si>
-  <si>
-    <t>0.03-0.16</t>
-  </si>
-  <si>
-    <t>0.05-0.17</t>
-  </si>
-  <si>
-    <t>0.04-0.19</t>
-  </si>
-  <si>
-    <t>0.08-0.18</t>
-  </si>
-  <si>
-    <t>0.04-0.17</t>
-  </si>
-  <si>
-    <t>0.09-0.19</t>
-  </si>
-  <si>
-    <t>0.09-0.25</t>
-  </si>
-  <si>
-    <t>0.11-0.22</t>
-  </si>
-  <si>
-    <t>0.08-0.15</t>
-  </si>
-  <si>
-    <t>0.08-0.19</t>
-  </si>
-  <si>
-    <t>3.00-6.00</t>
+    <t>Wrecked Ship Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Wrecked Ship on Shadow Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Shadow Plane</t>
+  </si>
+  <si>
+    <t>Wrecked Ship</t>
+  </si>
+  <si>
+    <t>Satans Cage Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Satans Cage on Hell, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Hell</t>
+  </si>
+  <si>
+    <t>Satans Cage</t>
+  </si>
+  <si>
+    <t>0.126-0.21</t>
+  </si>
+  <si>
+    <t>0.189-0.2625</t>
+  </si>
+  <si>
+    <t>Bandits Twisted Arm Port Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Bandits Twisted Arm Port on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Twisted Memories</t>
+  </si>
+  <si>
+    <t>Bandits Twisted Arm Port</t>
+  </si>
+  <si>
+    <t>0.3675-0.4515</t>
+  </si>
+  <si>
+    <t>0.504-0.6825</t>
+  </si>
+  <si>
+    <t>Church of God Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Church of God on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Church of God</t>
+  </si>
+  <si>
+    <t>Emerald Mining Town Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Emerald Mining Town on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Emerald Mining Town</t>
+  </si>
+  <si>
+    <t>Twisted Memorial Crypt Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Twisted Memorial Crypt on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Twisted Memorial Crypt</t>
+  </si>
+  <si>
+    <t>Twisted grave site Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Twisted grave site on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Twisted grave site</t>
+  </si>
+  <si>
+    <t>Abandoned Village Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Abandoned Village on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>The Ice Plane</t>
+  </si>
+  <si>
+    <t>Abandoned Village</t>
+  </si>
+  <si>
+    <t>0.2625-0.399</t>
+  </si>
+  <si>
+    <t>0.315-0.5775</t>
+  </si>
+  <si>
+    <t>Banshee Fields of Tomorrow Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Banshee Fields of Tomorrow on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Banshee Fields of Tomorrow</t>
+  </si>
+  <si>
+    <t>Bloody Snowman Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Bloody Snowman on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Bloody Snowman</t>
+  </si>
+  <si>
+    <t>Broken Forest Road Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Broken Forest Road on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Broken Forest Road</t>
+  </si>
+  <si>
+    <t>Frozen Pet Cemetary Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Frozen Pet Cemetary on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Frozen Pet Cemetary</t>
+  </si>
+  <si>
+    <t>Frozen Queens Bank Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Frozen Queens Bank on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Frozen Queens Bank</t>
+  </si>
+  <si>
+    <t>The Frozen Wreck Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for The Frozen Wreck on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>The Frozen Wreck</t>
+  </si>
+  <si>
+    <t>Abandonded Chapel Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Abandonded Chapel on Delusional Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Delusional Memories</t>
+  </si>
+  <si>
+    <t>Abandonded Chapel</t>
+  </si>
+  <si>
+    <t>Delusional Abandoned Gold Mines Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Delusional Abandoned Gold Mines on Delusional Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Delusional Abandoned Gold Mines</t>
+  </si>
+  <si>
+    <t>Federation Controlled Town Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Federation Controlled Town on Delusional Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Federation Controlled Town</t>
+  </si>
+  <si>
+    <t>Underwater Caves Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Underwater Caves on Surface, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Underwater Caves</t>
+  </si>
+  <si>
+    <t>Gold Mine Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Gold Mine on Shadow Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Gold Mine</t>
+  </si>
+  <si>
+    <t>Lords Stronghold Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Lords Stronghold on Shadow Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Lords Stronghold</t>
+  </si>
+  <si>
+    <t>Hells Broken Anvil Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Hells Broken Anvil on Hell, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Hells Broken Anvil</t>
+  </si>
+  <si>
+    <t>Tear in the Fabric of Time Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Tear in the Fabric of Time on Hell, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Tear in the Fabric of Time</t>
+  </si>
+  <si>
+    <t>Twisted Dimensional Gate Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Twisted Dimensional Gate on Hell, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Twisted Dimensional Gate</t>
+  </si>
+  <si>
+    <t>Cave of Memories Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Cave of Memories on Purgatory, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Cave of Memories</t>
+  </si>
+  <si>
+    <t>Purgatories Dungeons Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Purgatories Dungeons on Purgatory, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Purgatories Dungeons</t>
+  </si>
+  <si>
+    <t>Purgatory Smiths House Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Purgatory Smiths House on Purgatory, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Purgatory Smiths House</t>
+  </si>
+  <si>
+    <t>Cave of Shadows Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Cave of Shadows on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Cave of Shadows</t>
+  </si>
+  <si>
+    <t>Dungeons of the twisted maiden Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Dungeons of the twisted maiden on Twisted Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Dungeons of the twisted maiden</t>
+  </si>
+  <si>
+    <t>The Old Church Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for The Old Church on The Ice Plane, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>The Old Church</t>
+  </si>
+  <si>
+    <t>Alchemy Corrupted Church Gem Profile</t>
+  </si>
+  <si>
+    <t>Location gem profile for Alchemy Corrupted Church on Delusional Memories, raised five percent above its plane baseline.</t>
+  </si>
+  <si>
+    <t>Alchemy Corrupted Church</t>
   </si>
 </sst>
 </file>
@@ -615,47 +813,8 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="3.428" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="258.223" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="55.272" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="42.418" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="47.131" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="37.705" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="45.846" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="45.846" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="45.846" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="41.133" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="44.703" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="30" max="30" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="31" max="31" width="36.42" bestFit="true" customWidth="true" style="0"/>
-    <col min="32" max="32" width="51.845" bestFit="true" customWidth="true" style="0"/>
-    <col min="33" max="33" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="34" max="34" width="38.848" bestFit="true" customWidth="true" style="0"/>
-    <col min="35" max="35" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="36" max="36" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="37" max="37" width="28.136" bestFit="true" customWidth="true" style="0"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" t="s">
@@ -771,9 +930,6 @@
       </c>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
         <v>37</v>
       </c>
@@ -786,207 +942,3423 @@
       <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>46</v>
+        <v>41</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="W2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>42</v>
       </c>
       <c r="AF2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AG2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="AH2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:37">
-      <c r="A3">
-        <v>2</v>
-      </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="P3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>64</v>
+        <v>41</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="V3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="X3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="s">
-        <v>67</v>
+        <v>42</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>42</v>
       </c>
       <c r="AF3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AG3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AH3" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
-      <c r="A4">
-        <v>3</v>
-      </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W6" t="s">
+        <v>60</v>
+      </c>
+      <c r="X6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>66</v>
+      </c>
+      <c r="V7" t="s">
+        <v>66</v>
+      </c>
+      <c r="W7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" t="s">
+        <v>66</v>
+      </c>
+      <c r="W8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" t="s">
         <v>72</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" t="s">
+        <v>66</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="B10" t="s">
         <v>73</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C10" t="s">
         <v>74</v>
       </c>
-      <c r="G4" t="s">
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
         <v>75</v>
       </c>
-      <c r="H4" t="s">
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>66</v>
+      </c>
+      <c r="V10" t="s">
+        <v>66</v>
+      </c>
+      <c r="W10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="B11" t="s">
         <v>76</v>
       </c>
-      <c r="I4" t="s">
+      <c r="C11" t="s">
         <v>77</v>
       </c>
-      <c r="J4" t="s">
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
         <v>78</v>
       </c>
-      <c r="N4" t="s">
-        <v>76</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="P4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="U4" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="V4" t="s">
+      <c r="E12" t="s">
         <v>82</v>
       </c>
-      <c r="W4" t="s">
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" t="s">
+        <v>83</v>
+      </c>
+      <c r="O12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>84</v>
+      </c>
+      <c r="V12" t="s">
+        <v>84</v>
+      </c>
+      <c r="W12" t="s">
+        <v>84</v>
+      </c>
+      <c r="X12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
         <v>81</v>
       </c>
-      <c r="X4" t="s">
+      <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" t="s">
+        <v>83</v>
+      </c>
+      <c r="O13" t="s">
+        <v>83</v>
+      </c>
+      <c r="P13" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>84</v>
+      </c>
+      <c r="V13" t="s">
+        <v>84</v>
+      </c>
+      <c r="W13" t="s">
+        <v>84</v>
+      </c>
+      <c r="X13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O14" t="s">
+        <v>83</v>
+      </c>
+      <c r="P14" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>84</v>
+      </c>
+      <c r="V14" t="s">
+        <v>84</v>
+      </c>
+      <c r="W14" t="s">
+        <v>84</v>
+      </c>
+      <c r="X14" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
         <v>81</v>
       </c>
-      <c r="Z4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>86</v>
+      <c r="E15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" t="s">
+        <v>83</v>
+      </c>
+      <c r="N15" t="s">
+        <v>83</v>
+      </c>
+      <c r="O15" t="s">
+        <v>83</v>
+      </c>
+      <c r="P15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="s">
+        <v>84</v>
+      </c>
+      <c r="V15" t="s">
+        <v>84</v>
+      </c>
+      <c r="W15" t="s">
+        <v>84</v>
+      </c>
+      <c r="X15" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M16" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+      <c r="O16" t="s">
+        <v>83</v>
+      </c>
+      <c r="P16" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" t="s">
+        <v>84</v>
+      </c>
+      <c r="V16" t="s">
+        <v>84</v>
+      </c>
+      <c r="W16" t="s">
+        <v>84</v>
+      </c>
+      <c r="X16" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" t="s">
+        <v>83</v>
+      </c>
+      <c r="O17" t="s">
+        <v>83</v>
+      </c>
+      <c r="P17" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="s">
+        <v>84</v>
+      </c>
+      <c r="V17" t="s">
+        <v>84</v>
+      </c>
+      <c r="W17" t="s">
+        <v>84</v>
+      </c>
+      <c r="X17" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" t="s">
+        <v>83</v>
+      </c>
+      <c r="M18" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" t="s">
+        <v>83</v>
+      </c>
+      <c r="O18" t="s">
+        <v>83</v>
+      </c>
+      <c r="P18" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" t="s">
+        <v>84</v>
+      </c>
+      <c r="V18" t="s">
+        <v>84</v>
+      </c>
+      <c r="W18" t="s">
+        <v>84</v>
+      </c>
+      <c r="X18" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" t="s">
+        <v>65</v>
+      </c>
+      <c r="K19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" t="s">
+        <v>65</v>
+      </c>
+      <c r="P19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" t="s">
+        <v>66</v>
+      </c>
+      <c r="V19" t="s">
+        <v>66</v>
+      </c>
+      <c r="W19" t="s">
+        <v>66</v>
+      </c>
+      <c r="X19" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" t="s">
+        <v>65</v>
+      </c>
+      <c r="N20" t="s">
+        <v>65</v>
+      </c>
+      <c r="O20" t="s">
+        <v>65</v>
+      </c>
+      <c r="P20" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="s">
+        <v>66</v>
+      </c>
+      <c r="V20" t="s">
+        <v>66</v>
+      </c>
+      <c r="W20" t="s">
+        <v>66</v>
+      </c>
+      <c r="X20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="B21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" t="s">
+        <v>65</v>
+      </c>
+      <c r="J21" t="s">
+        <v>65</v>
+      </c>
+      <c r="K21" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N21" t="s">
+        <v>65</v>
+      </c>
+      <c r="O21" t="s">
+        <v>65</v>
+      </c>
+      <c r="P21" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" t="s">
+        <v>66</v>
+      </c>
+      <c r="V21" t="s">
+        <v>66</v>
+      </c>
+      <c r="W21" t="s">
+        <v>66</v>
+      </c>
+      <c r="X21" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" t="s">
+        <v>41</v>
+      </c>
+      <c r="O22" t="s">
+        <v>41</v>
+      </c>
+      <c r="P22" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22" t="s">
+        <v>42</v>
+      </c>
+      <c r="V22" t="s">
+        <v>42</v>
+      </c>
+      <c r="W22" t="s">
+        <v>42</v>
+      </c>
+      <c r="X22" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" t="s">
+        <v>42</v>
+      </c>
+      <c r="V23" t="s">
+        <v>42</v>
+      </c>
+      <c r="W23" t="s">
+        <v>42</v>
+      </c>
+      <c r="X23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="B24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>41</v>
+      </c>
+      <c r="M24" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24" t="s">
+        <v>41</v>
+      </c>
+      <c r="O24" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" t="s">
+        <v>42</v>
+      </c>
+      <c r="V24" t="s">
+        <v>42</v>
+      </c>
+      <c r="W24" t="s">
+        <v>42</v>
+      </c>
+      <c r="X24" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" t="s">
+        <v>59</v>
+      </c>
+      <c r="O25" t="s">
+        <v>59</v>
+      </c>
+      <c r="P25" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>60</v>
+      </c>
+      <c r="V25" t="s">
+        <v>60</v>
+      </c>
+      <c r="W25" t="s">
+        <v>60</v>
+      </c>
+      <c r="X25" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="B26" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" t="s">
+        <v>59</v>
+      </c>
+      <c r="O26" t="s">
+        <v>59</v>
+      </c>
+      <c r="P26" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" t="s">
+        <v>60</v>
+      </c>
+      <c r="V26" t="s">
+        <v>60</v>
+      </c>
+      <c r="W26" t="s">
+        <v>60</v>
+      </c>
+      <c r="X26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K27" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" t="s">
+        <v>59</v>
+      </c>
+      <c r="O27" t="s">
+        <v>59</v>
+      </c>
+      <c r="P27" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" t="s">
+        <v>60</v>
+      </c>
+      <c r="V27" t="s">
+        <v>60</v>
+      </c>
+      <c r="W27" t="s">
+        <v>60</v>
+      </c>
+      <c r="X27" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" t="s">
+        <v>83</v>
+      </c>
+      <c r="K28" t="s">
+        <v>83</v>
+      </c>
+      <c r="L28" t="s">
+        <v>83</v>
+      </c>
+      <c r="M28" t="s">
+        <v>83</v>
+      </c>
+      <c r="N28" t="s">
+        <v>83</v>
+      </c>
+      <c r="O28" t="s">
+        <v>83</v>
+      </c>
+      <c r="P28" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
+        <v>84</v>
+      </c>
+      <c r="V28" t="s">
+        <v>84</v>
+      </c>
+      <c r="W28" t="s">
+        <v>84</v>
+      </c>
+      <c r="X28" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" t="s">
+        <v>133</v>
+      </c>
+      <c r="E29" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" t="s">
+        <v>83</v>
+      </c>
+      <c r="K29" t="s">
+        <v>83</v>
+      </c>
+      <c r="L29" t="s">
+        <v>83</v>
+      </c>
+      <c r="M29" t="s">
+        <v>83</v>
+      </c>
+      <c r="N29" t="s">
+        <v>83</v>
+      </c>
+      <c r="O29" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>84</v>
+      </c>
+      <c r="V29" t="s">
+        <v>84</v>
+      </c>
+      <c r="W29" t="s">
+        <v>84</v>
+      </c>
+      <c r="X29" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K30" t="s">
+        <v>83</v>
+      </c>
+      <c r="L30" t="s">
+        <v>83</v>
+      </c>
+      <c r="M30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N30" t="s">
+        <v>83</v>
+      </c>
+      <c r="O30" t="s">
+        <v>83</v>
+      </c>
+      <c r="P30" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>84</v>
+      </c>
+      <c r="V30" t="s">
+        <v>84</v>
+      </c>
+      <c r="W30" t="s">
+        <v>84</v>
+      </c>
+      <c r="X30" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31" t="s">
+        <v>65</v>
+      </c>
+      <c r="K31" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" t="s">
+        <v>65</v>
+      </c>
+      <c r="P31" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>66</v>
+      </c>
+      <c r="V31" t="s">
+        <v>66</v>
+      </c>
+      <c r="W31" t="s">
+        <v>66</v>
+      </c>
+      <c r="X31" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
+      <c r="B32" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" t="s">
+        <v>65</v>
+      </c>
+      <c r="K32" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O32" t="s">
+        <v>65</v>
+      </c>
+      <c r="P32" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>66</v>
+      </c>
+      <c r="V32" t="s">
+        <v>66</v>
+      </c>
+      <c r="W32" t="s">
+        <v>66</v>
+      </c>
+      <c r="X32" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="B33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E33" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" t="s">
+        <v>83</v>
+      </c>
+      <c r="I33" t="s">
+        <v>83</v>
+      </c>
+      <c r="J33" t="s">
+        <v>83</v>
+      </c>
+      <c r="K33" t="s">
+        <v>83</v>
+      </c>
+      <c r="L33" t="s">
+        <v>83</v>
+      </c>
+      <c r="M33" t="s">
+        <v>83</v>
+      </c>
+      <c r="N33" t="s">
+        <v>83</v>
+      </c>
+      <c r="O33" t="s">
+        <v>83</v>
+      </c>
+      <c r="P33" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>84</v>
+      </c>
+      <c r="V33" t="s">
+        <v>84</v>
+      </c>
+      <c r="W33" t="s">
+        <v>84</v>
+      </c>
+      <c r="X33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37">
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" t="s">
+        <v>65</v>
+      </c>
+      <c r="J34" t="s">
+        <v>65</v>
+      </c>
+      <c r="K34" t="s">
+        <v>65</v>
+      </c>
+      <c r="L34" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" t="s">
+        <v>65</v>
+      </c>
+      <c r="N34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O34" t="s">
+        <v>65</v>
+      </c>
+      <c r="P34" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>66</v>
+      </c>
+      <c r="V34" t="s">
+        <v>66</v>
+      </c>
+      <c r="W34" t="s">
+        <v>66</v>
+      </c>
+      <c r="X34" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
